--- a/LAPORAN_LENGKAP_PITSTOP.xlsx
+++ b/LAPORAN_LENGKAP_PITSTOP.xlsx
@@ -459,12 +459,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>KM UPDATE WA</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>TANGGAL UPDATE WA</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>KM UPDATE WA</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -525,13 +525,13 @@
       <c r="H2" t="n">
         <v>112528</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="I2" t="n">
         <v>102528</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K2" t="n">
         <v>10000</v>
@@ -589,13 +589,13 @@
       <c r="H3" t="n">
         <v>30000</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="I3" t="n">
         <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -653,13 +653,13 @@
       <c r="H4" t="n">
         <v>30000</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="I4" t="n">
         <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -717,13 +717,13 @@
       <c r="H5" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="I5" t="n">
         <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -781,13 +781,13 @@
       <c r="H6" t="n">
         <v>10000</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="I6" t="n">
         <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
       <c r="H7" t="n">
         <v>30000</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="I7" t="n">
         <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
       <c r="H8" t="n">
         <v>200000</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="I8" t="n">
         <v>190000</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K8" t="n">
         <v>10000</v>
@@ -973,13 +973,13 @@
       <c r="H9" t="n">
         <v>20382</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="I9" t="n">
         <v>10382</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" t="n">
         <v>10000</v>
@@ -1037,13 +1037,13 @@
       <c r="H10" t="n">
         <v>129191</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="I10" t="n">
         <v>119191</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K10" t="n">
         <v>10000</v>
@@ -1101,13 +1101,13 @@
       <c r="H11" t="n">
         <v>10000</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="I11" t="n">
         <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
       <c r="H12" t="n">
         <v>235459</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="I12" t="n">
         <v>227459</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K12" t="n">
         <v>8000</v>
@@ -1227,13 +1227,13 @@
       <c r="H13" t="n">
         <v>152941</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="I13" t="n">
         <v>142941</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K13" t="n">
         <v>10000</v>
@@ -1291,13 +1291,13 @@
       <c r="H14" t="n">
         <v>167474</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="I14" t="n">
         <v>157474</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K14" t="n">
         <v>10000</v>
@@ -1355,13 +1355,13 @@
       <c r="H15" t="n">
         <v>299970</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+      <c r="I15" t="n">
         <v>289970</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K15" t="n">
         <v>10000</v>
@@ -1419,13 +1419,13 @@
       <c r="H16" t="n">
         <v>63440</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
+      <c r="I16" t="n">
         <v>53440</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K16" t="n">
         <v>10000</v>
@@ -1483,13 +1483,13 @@
       <c r="H17" t="n">
         <v>35000</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="I17" t="n">
         <v>20000</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K17" t="n">
         <v>15000</v>
@@ -1547,13 +1547,13 @@
       <c r="H18" t="n">
         <v>117157</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="I18" t="n">
         <v>107157</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K18" t="n">
         <v>10000</v>
@@ -1611,13 +1611,13 @@
       <c r="H19" t="n">
         <v>46426</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
+      <c r="I19" t="n">
         <v>31426</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K19" t="n">
         <v>15000</v>
@@ -1675,13 +1675,13 @@
       <c r="H20" t="n">
         <v>15000</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+      <c r="I20" t="n">
         <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1739,13 +1739,13 @@
       <c r="H21" t="n">
         <v>10000</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
+      <c r="I21" t="n">
         <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1803,13 +1803,13 @@
       <c r="H22" t="n">
         <v>102686</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
+      <c r="I22" t="n">
         <v>92686</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K22" t="n">
         <v>10000</v>
@@ -1867,13 +1867,13 @@
       <c r="H23" t="n">
         <v>242576</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+      <c r="I23" t="n">
         <v>232576</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K23" t="n">
         <v>10000</v>
@@ -1931,13 +1931,13 @@
       <c r="H24" t="n">
         <v>180450</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+      <c r="I24" t="n">
         <v>170450</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K24" t="n">
         <v>10000</v>
@@ -1995,13 +1995,13 @@
       <c r="H25" t="n">
         <v>151587</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>143542</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>2026-08-14 14:20</t>
         </is>
-      </c>
-      <c r="J25" t="n">
-        <v>143542</v>
       </c>
       <c r="K25" t="n">
         <v>8045</v>
@@ -2059,13 +2059,13 @@
       <c r="H26" t="n">
         <v>15000</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
+      <c r="I26" t="n">
         <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2123,13 +2123,13 @@
       <c r="H27" t="n">
         <v>113057</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
+      <c r="I27" t="n">
         <v>103057</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K27" t="n">
         <v>10000</v>
@@ -2187,13 +2187,13 @@
       <c r="H28" t="n">
         <v>10000</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
+      <c r="I28" t="n">
         <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2251,13 +2251,13 @@
       <c r="H29" t="n">
         <v>15000</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+      <c r="I29" t="n">
         <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
       <c r="H30" t="n">
         <v>136355</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
+      <c r="I30" t="n">
         <v>126355</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K30" t="n">
         <v>10000</v>
@@ -2379,13 +2379,13 @@
       <c r="H31" t="n">
         <v>11000</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
+      <c r="I31" t="n">
         <v>1000</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K31" t="n">
         <v>10000</v>
@@ -2443,13 +2443,13 @@
       <c r="H32" t="n">
         <v>15000</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
+      <c r="I32" t="n">
         <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2507,13 +2507,13 @@
       <c r="H33" t="n">
         <v>29301</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
+      <c r="I33" t="n">
         <v>19301</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K33" t="n">
         <v>10000</v>
@@ -2571,13 +2571,13 @@
       <c r="H34" t="n">
         <v>15000</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
+      <c r="I34" t="n">
         <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2635,13 +2635,13 @@
       <c r="H35" t="n">
         <v>70301</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>74497</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>2026-08-14 16:09</t>
         </is>
-      </c>
-      <c r="J35" t="n">
-        <v>74497</v>
       </c>
       <c r="K35" t="n">
         <v>-4196</v>
@@ -2699,13 +2699,13 @@
       <c r="H36" t="n">
         <v>292221</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
+      <c r="I36" t="n">
         <v>262221</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K36" t="n">
         <v>30000</v>
@@ -2763,13 +2763,13 @@
       <c r="H37" t="n">
         <v>120523</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
+      <c r="I37" t="n">
         <v>110523</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K37" t="n">
         <v>10000</v>
@@ -2827,13 +2827,13 @@
       <c r="H38" t="n">
         <v>211767</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
+      <c r="I38" t="n">
         <v>181767</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K38" t="n">
         <v>30000</v>
@@ -2891,13 +2891,13 @@
       <c r="H39" t="n">
         <v>29069</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
+      <c r="I39" t="n">
         <v>14069</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K39" t="n">
         <v>15000</v>
@@ -2955,13 +2955,13 @@
       <c r="H40" t="n">
         <v>257078</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
+      <c r="I40" t="n">
         <v>247078</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K40" t="n">
         <v>10000</v>
@@ -3019,13 +3019,13 @@
       <c r="H41" t="n">
         <v>188529</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
+      <c r="I41" t="n">
         <v>178529</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K41" t="n">
         <v>10000</v>
@@ -3083,13 +3083,13 @@
       <c r="H42" t="n">
         <v>197174</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
+      <c r="I42" t="n">
         <v>187174</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K42" t="n">
         <v>10000</v>
@@ -3147,13 +3147,13 @@
       <c r="H43" t="n">
         <v>109364</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
+      <c r="I43" t="n">
         <v>99364</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K43" t="n">
         <v>10000</v>
@@ -3211,13 +3211,13 @@
       <c r="H44" t="n">
         <v>158191</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
+      <c r="I44" t="n">
         <v>148191</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K44" t="n">
         <v>10000</v>
@@ -3275,13 +3275,13 @@
       <c r="H45" t="n">
         <v>96278</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
+      <c r="I45" t="n">
         <v>86278</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K45" t="n">
         <v>10000</v>
@@ -3339,13 +3339,13 @@
       <c r="H46" t="n">
         <v>78245</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
+      <c r="I46" t="n">
         <v>48245</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K46" t="n">
         <v>30000</v>
@@ -3403,13 +3403,13 @@
       <c r="H47" t="n">
         <v>92809</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
+      <c r="I47" t="n">
         <v>82809</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K47" t="n">
         <v>10000</v>
@@ -3467,13 +3467,13 @@
       <c r="H48" t="n">
         <v>99752</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
+      <c r="I48" t="n">
         <v>89752</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" t="n">
         <v>10000</v>
@@ -3531,13 +3531,13 @@
       <c r="H49" t="n">
         <v>10000</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="I49" t="n">
         <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3595,13 +3595,13 @@
       <c r="H50" t="n">
         <v>10000</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
+      <c r="I50" t="n">
         <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3659,13 +3659,13 @@
       <c r="H51" t="n">
         <v>130299</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
+      <c r="I51" t="n">
         <v>100299</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K51" t="n">
         <v>30000</v>
@@ -3723,13 +3723,13 @@
       <c r="H52" t="n">
         <v>75502</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
+      <c r="I52" t="n">
         <v>65502</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K52" t="n">
         <v>10000</v>
@@ -3787,13 +3787,13 @@
       <c r="H53" t="n">
         <v>75923</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
+      <c r="I53" t="n">
         <v>45923</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K53" t="n">
         <v>30000</v>
@@ -3851,13 +3851,13 @@
       <c r="H54" t="n">
         <v>275580</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
+      <c r="I54" t="n">
         <v>265580</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K54" t="n">
         <v>10000</v>
@@ -3915,13 +3915,13 @@
       <c r="H55" t="n">
         <v>85102</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
+      <c r="I55" t="n">
         <v>75102</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K55" t="n">
         <v>10000</v>
@@ -3979,13 +3979,13 @@
       <c r="H56" t="n">
         <v>217817</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
+      <c r="I56" t="n">
         <v>209817</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K56" t="n">
         <v>8000</v>
@@ -4041,13 +4041,13 @@
       <c r="H57" t="n">
         <v>43571</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
+      <c r="I57" t="n">
         <v>28571</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K57" t="n">
         <v>15000</v>
@@ -4105,13 +4105,13 @@
       <c r="H58" t="n">
         <v>159511</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
+      <c r="I58" t="n">
         <v>149511</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K58" t="n">
         <v>10000</v>
@@ -4169,13 +4169,13 @@
       <c r="H59" t="n">
         <v>15000</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
+      <c r="I59" t="n">
         <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -4233,13 +4233,13 @@
       <c r="H60" t="n">
         <v>15000</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
+      <c r="I60" t="n">
         <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
       <c r="H61" t="n">
         <v>210004</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
+      <c r="I61" t="n">
         <v>180004</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K61" t="n">
         <v>30000</v>
@@ -4361,13 +4361,13 @@
       <c r="H62" t="n">
         <v>89411</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
+      <c r="I62" t="n">
         <v>79411</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K62" t="n">
         <v>10000</v>
@@ -4425,13 +4425,13 @@
       <c r="H63" t="n">
         <v>51569</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
+      <c r="I63" t="n">
         <v>41569</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K63" t="n">
         <v>10000</v>
@@ -4489,13 +4489,13 @@
       <c r="H64" t="n">
         <v>15000</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
+      <c r="I64" t="n">
         <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
       <c r="H65" t="n">
         <v>48601</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
+      <c r="I65" t="n">
         <v>38601</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K65" t="n">
         <v>10000</v>
@@ -4617,13 +4617,13 @@
       <c r="H66" t="n">
         <v>77295</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
+      <c r="I66" t="n">
         <v>67295</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K66" t="n">
         <v>10000</v>
@@ -4681,13 +4681,13 @@
       <c r="H67" t="n">
         <v>64499</v>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
+      <c r="I67" t="n">
         <v>54499</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K67" t="n">
         <v>10000</v>
@@ -4745,13 +4745,13 @@
       <c r="H68" t="n">
         <v>44870</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
+      <c r="I68" t="n">
         <v>29870</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K68" t="n">
         <v>15000</v>
@@ -4809,13 +4809,13 @@
       <c r="H69" t="n">
         <v>116035</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
+      <c r="I69" t="n">
         <v>86035</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K69" t="n">
         <v>30000</v>
@@ -4873,13 +4873,13 @@
       <c r="H70" t="n">
         <v>31101</v>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
+      <c r="I70" t="n">
         <v>16101</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K70" t="n">
         <v>15000</v>
@@ -4937,13 +4937,13 @@
       <c r="H71" t="n">
         <v>174916</v>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
+      <c r="I71" t="n">
         <v>164916</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K71" t="n">
         <v>10000</v>
@@ -5001,13 +5001,13 @@
       <c r="H72" t="n">
         <v>209964</v>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
+      <c r="I72" t="n">
         <v>199964</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K72" t="n">
         <v>10000</v>
@@ -5065,13 +5065,13 @@
       <c r="H73" t="n">
         <v>170133</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
+      <c r="I73" t="n">
         <v>160133</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K73" t="n">
         <v>10000</v>
@@ -5127,13 +5127,13 @@
       <c r="H74" t="n">
         <v>81533</v>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
+      <c r="I74" t="n">
         <v>71533</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K74" t="n">
         <v>10000</v>
@@ -5191,13 +5191,13 @@
       <c r="H75" t="n">
         <v>93879</v>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>89259</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>2026-08-14 13:56</t>
         </is>
-      </c>
-      <c r="J75" t="n">
-        <v>89259</v>
       </c>
       <c r="K75" t="n">
         <v>4620</v>
@@ -5255,13 +5255,13 @@
       <c r="H76" t="n">
         <v>46047</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
+      <c r="I76" t="n">
         <v>31047</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K76" t="n">
         <v>15000</v>
@@ -5319,13 +5319,13 @@
       <c r="H77" t="n">
         <v>192112</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
+      <c r="I77" t="n">
         <v>162112</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K77" t="n">
         <v>30000</v>
@@ -5383,13 +5383,13 @@
       <c r="H78" t="n">
         <v>157649</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
+      <c r="I78" t="n">
         <v>147649</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K78" t="n">
         <v>10000</v>
@@ -5447,13 +5447,13 @@
       <c r="H79" t="n">
         <v>190430</v>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
+      <c r="I79" t="n">
         <v>180430</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K79" t="n">
         <v>10000</v>
@@ -5511,13 +5511,13 @@
       <c r="H80" t="n">
         <v>29578</v>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
+      <c r="I80" t="n">
         <v>14578</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K80" t="n">
         <v>15000</v>
@@ -5575,13 +5575,13 @@
       <c r="H81" t="n">
         <v>132368</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
+      <c r="I81" t="n">
         <v>122368</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K81" t="n">
         <v>10000</v>
@@ -5639,13 +5639,13 @@
       <c r="H82" t="n">
         <v>82940</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
+      <c r="I82" t="n">
         <v>72940</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K82" t="n">
         <v>10000</v>
@@ -5703,13 +5703,13 @@
       <c r="H83" t="n">
         <v>172701</v>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
+      <c r="I83" t="n">
         <v>142701</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K83" t="n">
         <v>30000</v>
@@ -5767,13 +5767,13 @@
       <c r="H84" t="n">
         <v>15000</v>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
+      <c r="I84" t="n">
         <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -5831,13 +5831,13 @@
       <c r="H85" t="n">
         <v>133704</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
+      <c r="I85" t="n">
         <v>123704</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K85" t="n">
         <v>10000</v>
@@ -5895,13 +5895,13 @@
       <c r="H86" t="n">
         <v>169061</v>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
+      <c r="I86" t="n">
         <v>159061</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K86" t="n">
         <v>10000</v>
@@ -5959,13 +5959,13 @@
       <c r="H87" t="n">
         <v>124469</v>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
+      <c r="I87" t="n">
         <v>114469</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K87" t="n">
         <v>10000</v>
@@ -6023,13 +6023,13 @@
       <c r="H88" t="n">
         <v>15000</v>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
+      <c r="I88" t="n">
         <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -6087,13 +6087,13 @@
       <c r="H89" t="n">
         <v>59658</v>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
+      <c r="I89" t="n">
         <v>44658</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K89" t="n">
         <v>15000</v>
@@ -6151,13 +6151,13 @@
       <c r="H90" t="n">
         <v>127997</v>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
+      <c r="I90" t="n">
         <v>117997</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K90" t="n">
         <v>10000</v>
@@ -6215,13 +6215,13 @@
       <c r="H91" t="n">
         <v>160536</v>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
+      <c r="I91" t="n">
         <v>150536</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K91" t="n">
         <v>10000</v>
@@ -6279,13 +6279,13 @@
       <c r="H92" t="n">
         <v>344721</v>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
+      <c r="I92" t="n">
         <v>334721</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K92" t="n">
         <v>10000</v>
@@ -6343,13 +6343,13 @@
       <c r="H93" t="n">
         <v>209724</v>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
+      <c r="I93" t="n">
         <v>199724</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K93" t="n">
         <v>10000</v>
@@ -6407,13 +6407,13 @@
       <c r="H94" t="n">
         <v>202219</v>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
+      <c r="I94" t="n">
         <v>192219</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K94" t="n">
         <v>10000</v>
@@ -6471,13 +6471,13 @@
       <c r="H95" t="n">
         <v>234452</v>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
+      <c r="I95" t="n">
         <v>224452</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K95" t="n">
         <v>10000</v>
@@ -6535,13 +6535,13 @@
       <c r="H96" t="n">
         <v>70334</v>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
+      <c r="I96" t="n">
         <v>40334</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K96" t="n">
         <v>30000</v>
@@ -6599,13 +6599,13 @@
       <c r="H97" t="n">
         <v>139680</v>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
+      <c r="I97" t="n">
         <v>109680</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K97" t="n">
         <v>30000</v>
@@ -6663,13 +6663,13 @@
       <c r="H98" t="n">
         <v>94932</v>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
+      <c r="I98" t="n">
         <v>84932</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K98" t="n">
         <v>10000</v>
@@ -6727,13 +6727,13 @@
       <c r="H99" t="n">
         <v>94241</v>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
+      <c r="I99" t="n">
         <v>84241</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K99" t="n">
         <v>10000</v>
@@ -6791,13 +6791,13 @@
       <c r="H100" t="n">
         <v>110084</v>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
+      <c r="I100" t="n">
         <v>100084</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K100" t="n">
         <v>10000</v>
@@ -6855,13 +6855,13 @@
       <c r="H101" t="n">
         <v>30000</v>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
+      <c r="I101" t="n">
         <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -6919,13 +6919,13 @@
       <c r="H102" t="n">
         <v>188291</v>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
+      <c r="I102" t="n">
         <v>178291</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K102" t="n">
         <v>10000</v>
@@ -6983,13 +6983,13 @@
       <c r="H103" t="n">
         <v>194939</v>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
+      <c r="I103" t="n">
         <v>184939</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K103" t="n">
         <v>10000</v>
@@ -7047,13 +7047,13 @@
       <c r="H104" t="n">
         <v>265804</v>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
+      <c r="I104" t="n">
         <v>255804</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K104" t="n">
         <v>10000</v>
@@ -7111,13 +7111,13 @@
       <c r="H105" t="n">
         <v>10000</v>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
+      <c r="I105" t="n">
         <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -7175,13 +7175,13 @@
       <c r="H106" t="n">
         <v>90531</v>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
+      <c r="I106" t="n">
         <v>60531</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K106" t="n">
         <v>30000</v>
@@ -7239,13 +7239,13 @@
       <c r="H107" t="n">
         <v>325029</v>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
+      <c r="I107" t="n">
         <v>317029</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K107" t="n">
         <v>8000</v>
@@ -7301,13 +7301,13 @@
       <c r="H108" t="n">
         <v>156976</v>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
+      <c r="I108" t="n">
         <v>146976</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K108" t="n">
         <v>10000</v>
@@ -7365,13 +7365,13 @@
       <c r="H109" t="n">
         <v>153073</v>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
+      <c r="I109" t="n">
         <v>123073</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K109" t="n">
         <v>30000</v>
@@ -7429,13 +7429,13 @@
       <c r="H110" t="n">
         <v>300194</v>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
+      <c r="I110" t="n">
         <v>292194</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K110" t="n">
         <v>8000</v>
@@ -7491,13 +7491,13 @@
       <c r="H111" t="n">
         <v>91630</v>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
+      <c r="I111" t="n">
         <v>81630</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K111" t="n">
         <v>10000</v>
@@ -7555,13 +7555,13 @@
       <c r="H112" t="n">
         <v>10000</v>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
+      <c r="I112" t="n">
         <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -7619,13 +7619,13 @@
       <c r="H113" t="n">
         <v>86309</v>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" t="n">
+        <v>85375</v>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>2026-08-14 16:07</t>
         </is>
-      </c>
-      <c r="J113" t="n">
-        <v>85375</v>
       </c>
       <c r="K113" t="n">
         <v>934</v>
@@ -7683,13 +7683,13 @@
       <c r="H114" t="n">
         <v>119882</v>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
+      <c r="I114" t="n">
         <v>109882</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K114" t="n">
         <v>10000</v>
@@ -7747,13 +7747,13 @@
       <c r="H115" t="n">
         <v>179384</v>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
+      <c r="I115" t="n">
         <v>169384</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K115" t="n">
         <v>10000</v>
@@ -7811,13 +7811,13 @@
       <c r="H116" t="n">
         <v>181922</v>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
+      <c r="I116" t="n">
         <v>171922</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K116" t="n">
         <v>10000</v>
@@ -7875,13 +7875,13 @@
       <c r="H117" t="n">
         <v>344441</v>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
+      <c r="I117" t="n">
         <v>334441</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K117" t="n">
         <v>10000</v>
@@ -7939,13 +7939,13 @@
       <c r="H118" t="n">
         <v>316084</v>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" t="n">
+        <v>310032</v>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>2026-08-14 15:43</t>
         </is>
-      </c>
-      <c r="J118" t="n">
-        <v>310032</v>
       </c>
       <c r="K118" t="n">
         <v>6052</v>
@@ -8001,13 +8001,13 @@
       <c r="H119" t="n">
         <v>295132</v>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
+      <c r="I119" t="n">
         <v>285132</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K119" t="n">
         <v>10000</v>
@@ -8065,13 +8065,13 @@
       <c r="H120" t="n">
         <v>187242</v>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
+      <c r="I120" t="n">
         <v>177242</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K120" t="n">
         <v>10000</v>
@@ -8129,13 +8129,13 @@
       <c r="H121" t="n">
         <v>91447</v>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
+      <c r="I121" t="n">
         <v>81447</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K121" t="n">
         <v>10000</v>
@@ -8193,13 +8193,13 @@
       <c r="H122" t="n">
         <v>138679</v>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
+      <c r="I122" t="n">
         <v>128679</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K122" t="n">
         <v>10000</v>
@@ -8257,13 +8257,13 @@
       <c r="H123" t="n">
         <v>157195</v>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
+      <c r="I123" t="n">
         <v>147195</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K123" t="n">
         <v>10000</v>
@@ -8321,13 +8321,13 @@
       <c r="H124" t="n">
         <v>145954</v>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
+      <c r="I124" t="n">
         <v>135954</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K124" t="n">
         <v>10000</v>
